--- a/results/job_matches_2026-09-25.xlsx
+++ b/results/job_matches_2026-09-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eHealth</t>
+          <t>MOXFIVE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, BigQuery</t>
+          <t>AWS, Glue, Athena, S3, Azure, Synapse Analytics, Databricks, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f6705aae6b6275d</t>
+          <t>https://www.indeed.com/viewjob?jk=03e682d983ea38fa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SPEC ADV SOFTWARE ENGINEER</t>
+          <t>Senior Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54cc75b0d6eba6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f84f00ddd01d5e6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Magento Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b60177884abfc7</t>
+          <t>https://www.indeed.com/viewjob?jk=146beab3fdc4d479</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOXFIVE</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, Azure, Synapse Analytics, Databricks, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Data Modeling, ELT, MLflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e682d983ea38fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6a436017e20a9af4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
+          <t>Senior SDET I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>American Fork, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f84f00ddd01d5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd9f6a88f947060</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Magento Architect</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=146beab3fdc4d479</t>
+          <t>https://www.indeed.com/viewjob?jk=2287ae354f1f523a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WebMobi 360</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3166815bf9267880</t>
+          <t>https://www.indeed.com/viewjob?jk=818d7c1abdb2887e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2287ae354f1f523a</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddd1a1b90b2718b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Personify Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,52 +766,52 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818d7c1abdb2887e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f159b8174b6d797</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e200e28931966534</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b1ed692066ba92</t>
         </is>
       </c>
     </row>
@@ -853,60 +853,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Data Product Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Data Factory, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9977f0a1555dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c24c8142ac8427</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Mobilunity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, BigQuery, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c7d9bcaaeb50a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a02158bbc6c5b14c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Information Data Architect (HYBRID)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Giant Eagle</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Howell, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Databricks, Medallion Architecture, Dataflow, Hive, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838bd05b65e5a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=68c604ade259ccaa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Product Engineer</t>
+          <t>Associate Information Data Architect (HYBRID)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Windsor, CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Data Factory, Scala</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c24c8142ac8427</t>
+          <t>https://www.indeed.com/viewjob?jk=118ebf151550d94c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Associate Information Data Architect (HYBRID)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mobilunity</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, BigQuery, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02158bbc6c5b14c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7ae1d0f1d7773c</t>
         </is>
       </c>
     </row>
@@ -1063,52 +1063,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Information Data Architect (HYBRID)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d939162f62431c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=5af1d8c0bb95e882</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer – Physical AI Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Apex Companies, LLC</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b824421b414861d1</t>
+          <t>https://www.indeed.com/viewjob?jk=292f16b23875be76</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c65ed1f8238807</t>
+          <t>https://www.indeed.com/viewjob?jk=d939162f62431c6d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Apex Companies, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, ETL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5602865a9185ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b824421b414861d1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer</t>
+          <t>Software Engineer, Data (L2)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Delta Dental</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8df16d0ff3f6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c65ed1f8238807</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fcbe657bfdd87d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5602865a9185ab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Backend Engineer: Retail Media</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Constructor</t>
+          <t>Skanska</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31b9608c06c91b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d57fb86a5ed9c4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer Sr (ETL/Alteryx)</t>
+          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=5af48e8af3978cdd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Databricks Administrator</t>
+          <t>Data Engineer Sr (ETL/Alteryx)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Spark, PySpark, Databricks Lakehouse</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa309349753fd7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>Azure Databricks Administrator</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Spark, PySpark, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea65c9a95c2f071</t>
+          <t>https://www.indeed.com/viewjob?jk=aa309349753fd7ab</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Operations Analyst (Oracle)</t>
+          <t>Sr. Software Engineer - Core Automation Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904eb88b47275924</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea65c9a95c2f071</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5f5f93a058e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5662b2a7e9c297d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71df1cf7ba215399</t>
+          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hirschi Companies, LLC</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>North Las Vegas, NV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Star Schema, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ea9ea264ebb9e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5f5f93a058e1e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer - FinOps (100% Remote)</t>
+          <t>Senior Partner Solutions Architect – GSI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>Wiz Soluções</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88877cf6fea16493</t>
+          <t>https://www.indeed.com/viewjob?jk=8072ceac30ce67e5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Architecture (100% Remote)</t>
+          <t>Sr Business Analyst, Applied Intelligence</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9f4b4e6bfc1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior DevOps</t>
+          <t>Enterprise Data &amp; AI Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AltexSoft</t>
+          <t>Hirschi Companies, LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Star Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a491606b996c9fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=9ea9ea264ebb9e6f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Data Engineer, Data Platform</t>
+          <t>Associate DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ｃollective</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Data Modeling, Dimensional Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020174f364165c18</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0b22901658da1c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Edwardsville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15662d40b4bb4797</t>
+          <t>https://www.indeed.com/viewjob?jk=ba91948089d6225f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior DevOps</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>AltexSoft</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652bceb12bdc8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=a491606b996c9fd4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>DevOps Engineer - FinOps (100% Remote)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0e14623092813</t>
+          <t>https://www.indeed.com/viewjob?jk=88877cf6fea16493</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>DevOps Engineer - Architecture (100% Remote)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfd599f9976074a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9f4b4e6bfc1b44</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ceb5e692edcab9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac2005fd12c4ec8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>AI Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Ｃollective</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Data Modeling, Dimensional Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70c97558041cbb3</t>
+          <t>https://www.indeed.com/viewjob?jk=020174f364165c18</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Microsoft Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, DataOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44465103a210f6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>POSH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2b9d01e6a420aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ec04f06f37703a72</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer(Azure) at Major Japanese Bank</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Sibanye Stillwater</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fairless Hills, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd631b20e53bc138</t>
+          <t>https://www.indeed.com/viewjob?jk=980adf77ba3c35d4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Edwardsville, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac853620a7883a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=15662d40b4bb4797</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Data Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d60ea38d35340ba</t>
+          <t>https://www.indeed.com/viewjob?jk=652bceb12bdc8ca1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack Applications (Python &amp; React)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, NoSQL, dbt, Amazon QuickSight, Power BI, MLOps, CI/CD, Terraform</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab6da126dcb613</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0e14623092813</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, dbt, Power BI, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41698f714a5488d9</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfd599f9976074a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=83ceb5e692edcab9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Service Developer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, Scala, Snowflake, NoSQL, ETL, Docker</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac560d1fcf55c4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d70c97558041cbb3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, AWS, Spark)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f4ce506118a2862</t>
+          <t>https://www.indeed.com/viewjob?jk=44465103a210f6ed</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Oats Overnight</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,137 +2281,137 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a248bb83a45531e</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2b9d01e6a420aa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Typescript/Nodejs/Python)</t>
+          <t>Data Engineer(Azure) at Major Japanese Bank</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bf87e39f33644</t>
+          <t>https://www.indeed.com/viewjob?jk=fd631b20e53bc138</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426b656990b6c0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac853620a7883a2f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (GraphDB &amp; API Platform) (Enterprise Platforms Technology)</t>
+          <t>AI Data Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a5f6a97115f8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d60ea38d35340ba</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Scientist New College Grad- Bachelor's/Master's (Austin, TX)</t>
+          <t>Senior Software Engineer- full stack Java</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4dc7483cb11054</t>
+          <t>https://www.indeed.com/viewjob?jk=390092f6c0217007</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AWS Cloud Infrastructure</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines, Inc.</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42296d5e5f61808</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8918c1adb526db</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Engineer 4 (Cloud Security for Multi Cloud) (Cloud Operations Resilience Engineering)</t>
+          <t>Senior Software Development Engineer - Microservices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e90d49deb28c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ed0115e6583c60</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Kubernetes Platform Engineer</t>
+          <t>Senior Software Development Engineer - Microservices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Silicon Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b345fefbec3728e4</t>
+          <t>https://www.indeed.com/viewjob?jk=beb4540fc449cc54</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - CloudOps</t>
+          <t>Senior Software Engineer, Full-Stack Applications (Python &amp; React)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AAA Auto Club Enterprises</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD, CodeBuild</t>
+          <t>AWS, Spark, Scala, NoSQL, dbt, Amazon QuickSight, Power BI, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f63884918300be</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab6da126dcb613</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,94 +2596,94 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4bd4a90683613e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>Senior Data Service Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, ETL, ELT, dbt, Power BI, Docker, Airflow</t>
+          <t>AWS, Redshift, S3, Azure, GCP, Scala, Snowflake, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547f52225d0ee37c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac560d1fcf55c4e3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Palantir IT Developer</t>
+          <t>Software Engineer- full stack Java</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shoals Technologies Group</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Data Modeling, ETL, Power BI, Tableau, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ef97641045d2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=66f81aa15390f51b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Oats Overnight</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0315e75878b9523</t>
+          <t>https://www.indeed.com/viewjob?jk=6a248bb83a45531e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Full-stack Engineer 5 (Typescript/Nodejs/Python)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CareConnectMD</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, MySQL, Data Modeling, Power BI, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbf87ce3ecaa2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a42bf87e39f33644</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1f8022341fbeec</t>
+          <t>https://www.indeed.com/viewjob?jk=426b656990b6c0b5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5 (GraphDB &amp; API Platform) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2801,29 +2801,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de05f9c575d914fd</t>
+          <t>https://www.indeed.com/viewjob?jk=07a5f6a97115f8a1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,112 +2831,112 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, MicroStrategy, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e52d983dd64d153</t>
+          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b731d4dc3bbcac</t>
+          <t>https://www.indeed.com/viewjob?jk=695ee016a6862deb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend II (Intern) â€“ United States</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6524e36b7c2e899e</t>
+          <t>https://www.indeed.com/viewjob?jk=74dc88aa87ede3c8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Application Engineer (FIS Systematics/ ALS)</t>
+          <t>Data Scientist New College Grad- Bachelor's/Master's (Austin, TX)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Oracle, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,49 +2946,49 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f1cd08763c029e</t>
+          <t>https://www.indeed.com/viewjob?jk=de4dc7483cb11054</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 - MLOps</t>
+          <t>Senior Software Engineer, AWS Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Praxis Precision Medicines, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, MLOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=f42296d5e5f61808</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
+          <t>Cloud Engineer 4 (Cloud Security for Multi Cloud) (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3002,221 +3002,221 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
+          <t>https://www.indeed.com/viewjob?jk=465e90d49deb28c0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+          <t>Sr. Kubernetes Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Silicon Labs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b345fefbec3728e4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+          <t>IT Developer Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chippewa Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc9fb81e98d2ad5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
+          <t>Senior Java Spring Boot Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
+          <t>https://www.indeed.com/viewjob?jk=323842bd0f86343f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, dbt, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85feb7d306b29d57</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4c01cee06410c3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Loudoun County, VA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Oracle, SQL Server, ETL, CI/CD, Git</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,94 +3226,94 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e717b40d7b736c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0315e75878b9523</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II - Insights, Strategy &amp; Analysis</t>
+          <t>IT Data Solutions Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sony Pictures Entertainment</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, ELT, dbt, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6982cb40c81de86</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1f8022341fbeec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
+          <t>Data Visualization Engineer 1 4P/846</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Liberty company insurance brokers</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Forest Park, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c74794261ba4cf1b</t>
+          <t>https://www.indeed.com/viewjob?jk=32c5956a500a065e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer .NET</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0c3fa28fe6f12d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b731d4dc3bbcac</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer</t>
+          <t>Software Engineer Full Stack / Backend II (Intern) â€“ United States</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wider Circle</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Scala, ETL, ELT, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1d7f71ee4bde2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6524e36b7c2e899e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
+          <t>Senior Application Engineer (FIS Systematics/ ALS)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Oracle, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f1cd08763c029e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IT Architect – Cloud Platform</t>
+          <t>Full Stack Engineer 4 - MLOps</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, MLOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed1caebc6240c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Engineer 5 (IC)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c91ca59322d0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data QA Engineer</t>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4debc3d900a917c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, SecOps</t>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cambridge Mobile Telematics</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c903ba36fc2337b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Enterprise Software Architect</t>
+          <t>Full-Stack Engineer 4 (Risk Tech)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>America First Credit Union</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ogden, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,507 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Scala, NoSQL, CI/CD, Jenkins, Kubernetes, Jenkins, Git, Bitbucket</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac80251d3b26ae94</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 5 (IC)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, dbt, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85feb7d306b29d57</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Cloud BigData Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Delan Associates, Inc</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59ab60d145780389</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Payabli</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76b9fbb8b5a5e806</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Payabli</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62b3077cbdbcc197</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, dbt, Tableau, CI/CD, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bc2fb0114a4b756</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Loudoun County, VA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Leesburg, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Oracle, SQL Server, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e717b40d7b736c3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=995dd503c97eb758</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>.Net Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94999510187cc616</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Engineer .NET</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0c3fa28fe6f12d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Havenpark Communities</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Orem, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08a26f25fa395039</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7c91ca59322d0ce</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-25.xlsx
+++ b/results/job_matches_2026-09-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
+          <t>Senior Magento Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f84f00ddd01d5e6</t>
+          <t>https://www.indeed.com/viewjob?jk=146beab3fdc4d479</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Magento Architect</t>
+          <t>Data Engineer 4 (Python, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=146beab3fdc4d479</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec4e00003379849</t>
         </is>
       </c>
     </row>
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior SDET I</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, Splunk</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd9f6a88f947060</t>
+          <t>https://www.indeed.com/viewjob?jk=fea69319765aa1cc</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, AWS, SQL, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818d7c1abdb2887e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddd1a1b90b2718b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Personify Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddd1a1b90b2718b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f159b8174b6d797</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Personify Health</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f159b8174b6d797</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b1ed692066ba92</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b1ed692066ba92</t>
+          <t>https://www.indeed.com/viewjob?jk=5752c0fe726daa2e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Product Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Data Factory, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5752c0fe726daa2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c24c8142ac8427</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Product Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Mobilunity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Data Factory, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, BigQuery, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c24c8142ac8427</t>
+          <t>https://www.indeed.com/viewjob?jk=a02158bbc6c5b14c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Associate Information Data Architect (HYBRID)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mobilunity</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Howell, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, BigQuery, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02158bbc6c5b14c</t>
+          <t>https://www.indeed.com/viewjob?jk=68c604ade259ccaa</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Howell, MI, US USA</t>
+          <t>Windsor, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c604ade259ccaa</t>
+          <t>https://www.indeed.com/viewjob?jk=118ebf151550d94c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Windsor, CT, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ebf151550d94c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7ae1d0f1d7773c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate Information Data Architect (HYBRID)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7ae1d0f1d7773c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f466c8c66d72247</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Information Data Architect (HYBRID)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,52 +1046,52 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f466c8c66d72247</t>
+          <t>https://www.indeed.com/viewjob?jk=5af1d8c0bb95e882</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Information Data Architect (HYBRID)</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af1d8c0bb95e882</t>
+          <t>https://www.indeed.com/viewjob?jk=de31c40d2a0ecf08</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Skanska</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d57fb86a5ed9c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Skanska</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af48e8af3978cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d57fb86a5ed9c4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer Sr (ETL/Alteryx)</t>
+          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=5af48e8af3978cdd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Databricks Administrator</t>
+          <t>Sr. Data Engineer, Financial Systems (Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Spark, PySpark, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa309349753fd7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d4cee9cb47e0f3e3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>Senior Architect, Healthcare Payer Domain</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, ECS, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea65c9a95c2f071</t>
+          <t>https://www.indeed.com/viewjob?jk=ed88a3a19664a4ab</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Data Engineer Sr (ETL/Alteryx)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Tableau, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5662b2a7e9c297d</t>
+          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5662b2a7e9c297d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5f5f93a058e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=15797458cef00167</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Partner Solutions Architect – GSI</t>
+          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wiz Soluções</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8072ceac30ce67e5</t>
+          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Business Analyst, Applied Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Star Schema</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5f5f93a058e1e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Architect</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hirschi Companies, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>North Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Star Schema, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ea9ea264ebb9e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=0902a69e0fc5e870</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate DevOps Engineer</t>
+          <t>Senior Partner Solutions Architect – GSI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Wiz Soluções</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0b22901658da1c</t>
+          <t>https://www.indeed.com/viewjob?jk=8072ceac30ce67e5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr Business Analyst, Applied Intelligence</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Star Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba91948089d6225f</t>
+          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps</t>
+          <t>Enterprise Data &amp; AI Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AltexSoft</t>
+          <t>Hirschi Companies, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Star Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a491606b996c9fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=9ea9ea264ebb9e6f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer - FinOps (100% Remote)</t>
+          <t>Senior DevOps</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>AltexSoft</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88877cf6fea16493</t>
+          <t>https://www.indeed.com/viewjob?jk=a491606b996c9fd4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Architecture (100% Remote)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9f4b4e6bfc1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=ba91948089d6225f</t>
         </is>
       </c>
     </row>
@@ -1868,25 +1868,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Data Engineer, Data Platform</t>
+          <t>Associate DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ｃollective</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Data Modeling, Dimensional Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020174f364165c18</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0b22901658da1c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Platform Engineer</t>
+          <t>AI Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Ｃollective</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, DataOps, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Data Modeling, Dimensional Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
+          <t>https://www.indeed.com/viewjob?jk=020174f364165c18</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Microsoft Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>POSH</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, DataOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec04f06f37703a72</t>
+          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sibanye Stillwater</t>
+          <t>POSH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fairless Hills, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=980adf77ba3c35d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec04f06f37703a72</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Sibanye Stillwater</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Edwardsville, IL, US USA</t>
+          <t>Fairless Hills, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15662d40b4bb4797</t>
+          <t>https://www.indeed.com/viewjob?jk=980adf77ba3c35d4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Edwardsville, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652bceb12bdc8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=15662d40b4bb4797</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0e14623092813</t>
+          <t>https://www.indeed.com/viewjob?jk=652bceb12bdc8ca1</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfd599f9976074a</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0e14623092813</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ceb5e692edcab9</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfd599f9976074a</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70c97558041cbb3</t>
+          <t>https://www.indeed.com/viewjob?jk=83ceb5e692edcab9</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44465103a210f6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d70c97558041cbb3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2b9d01e6a420aa</t>
+          <t>https://www.indeed.com/viewjob?jk=44465103a210f6ed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer(Azure) at Major Japanese Bank</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd631b20e53bc138</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2b9d01e6a420aa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Data Engineer(Azure) at Major Japanese Bank</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, dbt, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac853620a7883a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd631b20e53bc138</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Data Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d60ea38d35340ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ac853620a7883a2f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- full stack Java</t>
+          <t>AI Data Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=390092f6c0217007</t>
+          <t>https://www.indeed.com/viewjob?jk=6d60ea38d35340ba</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer (175879)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8918c1adb526db</t>
+          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Microservices</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Skanska</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ed0115e6583c60</t>
+          <t>https://www.indeed.com/viewjob?jk=3a5364385227f4cc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Microservices</t>
+          <t>Senior Software Engineer- full stack Java</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb4540fc449cc54</t>
+          <t>https://www.indeed.com/viewjob?jk=390092f6c0217007</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack Applications (Python &amp; React)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, NoSQL, dbt, Amazon QuickSight, Power BI, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab6da126dcb613</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8918c1adb526db</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior Software Development Engineer - Microservices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ed0115e6583c60</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Service Developer</t>
+          <t>Senior Software Development Engineer - Microservices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, Scala, Snowflake, NoSQL, ETL, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac560d1fcf55c4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=beb4540fc449cc54</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer- full stack Java</t>
+          <t>Senior Software Engineer, Full-Stack Applications (Python &amp; React)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Spark, Scala, NoSQL, dbt, Amazon QuickSight, Power BI, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f81aa15390f51b</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab6da126dcb613</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Service Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Oats Overnight</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, S3, Azure, GCP, Scala, Snowflake, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,49 +2701,49 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a248bb83a45531e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac560d1fcf55c4e3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Typescript/Nodejs/Python)</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42bf87e39f33644</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Java, Python, AWS, Spark)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,77 +2753,77 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426b656990b6c0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b838d14974b57715</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (GraphDB &amp; API Platform) (Enterprise Platforms Technology)</t>
+          <t>Software Engineer- full stack Java</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a5f6a97115f8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=66f81aa15390f51b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Oats Overnight</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, MicroStrategy, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
+          <t>https://www.indeed.com/viewjob?jk=6a248bb83a45531e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, MicroStrategy, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695ee016a6862deb</t>
+          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74dc88aa87ede3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=695ee016a6862deb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist New College Grad- Bachelor's/Master's (Austin, TX)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4dc7483cb11054</t>
+          <t>https://www.indeed.com/viewjob?jk=74dc88aa87ede3c8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AWS Cloud Infrastructure</t>
+          <t>Data Scientist New College Grad- Bachelor's/Master's (Austin, TX)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines, Inc.</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42296d5e5f61808</t>
+          <t>https://www.indeed.com/viewjob?jk=de4dc7483cb11054</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Engineer 4 (Cloud Security for Multi Cloud) (Cloud Operations Resilience Engineering)</t>
+          <t>Senior Software Engineer, AWS Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Praxis Precision Medicines, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e90d49deb28c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f42296d5e5f61808</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Kubernetes Platform Engineer</t>
+          <t>Cloud Engineer 4 (Cloud Security for Multi Cloud) (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Silicon Labs</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b345fefbec3728e4</t>
+          <t>https://www.indeed.com/viewjob?jk=465e90d49deb28c0</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chippewa Falls, WI, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Visualization Engineer 1 4P/846</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Forest Park, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0315e75878b9523</t>
+          <t>https://www.indeed.com/viewjob?jk=32c5956a500a065e</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer 1 4P/846</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Forest Park, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c5956a500a065e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0315e75878b9523</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b731d4dc3bbcac</t>
+          <t>https://www.indeed.com/viewjob?jk=206f2f5d1f1047a7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend II (Intern) â€“ United States</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6524e36b7c2e899e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce4fb53c85b4ee0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Application Engineer (FIS Systematics/ ALS)</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS, CI/CD, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Oracle, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f1cd08763c029e</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd4877047c7d1ba</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 - MLOps</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,32 +3418,32 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, MLOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be9e63b1f034fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=9f51686d020df00d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c64a6b657bec041</t>
+          <t>https://www.indeed.com/viewjob?jk=c4dabfb5c32f0281</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+          <t>Full-stack Engineer 4 (Node, TypeScript, AWS)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3492,28 +3492,28 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77ef5d6712f79e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d12d10b908918fa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2099af0bd18f2a89</t>
+          <t>https://www.indeed.com/viewjob?jk=bc673ca517807c08</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Risk Tech)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,32 +3558,32 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4615688d3aeae7</t>
+          <t>https://www.indeed.com/viewjob?jk=7c8a5b6d5542fa2c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer 5 (IC)</t>
+          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3597,151 +3597,151 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Dask, CI/CD, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be872dbf08ff65ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb745dca3323ff8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Reston, VA - Freewheel</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Snowflake, dbt, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85feb7d306b29d57</t>
+          <t>https://www.indeed.com/viewjob?jk=c5892e9800b1f76b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud BigData Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Go, CI/CD, AWS)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ab60d145780389</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f69dde706e3448</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
+          <t>https://www.indeed.com/viewjob?jk=53d4dc84b85c3670</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b9fbb8b5a5e806</t>
+          <t>https://www.indeed.com/viewjob?jk=9888eedf29cfd51f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Full-stack Engineer 4 (Java/Python, IaC, AWS)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b3077cbdbcc197</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cadf1933502029</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, dbt, Tableau, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc2fb0114a4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=843ce198c1c04576</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Loudoun County, VA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Oracle, SQL Server, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e717b40d7b736c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ff04ef4604e476c6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dd503c97eb758</t>
+          <t>https://www.indeed.com/viewjob?jk=fecc6c5f25f41ffc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>.Net Architect</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94999510187cc616</t>
+          <t>https://www.indeed.com/viewjob?jk=d48d24e36571ac6e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Engineer .NET</t>
+          <t>Full Stack Engineer 4 (Bank Tech)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0c3fa28fe6f12d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2a2c8569c5046b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Havenpark Communities</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,77 +3996,882 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a26f25fa395039</t>
+          <t>https://www.indeed.com/viewjob?jk=e410790f9b462e9f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=52108bbcbb003e69</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0cdc8d34a934bbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=138e060c9ff0d615</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (AI / ML) - Spring 2027</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aefb70733fd4805b</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Integration Engineer 4 - Payment Network Partner Experience</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41e45723ef8f4f70</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - VAULT</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9b731d4dc3bbcac</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer Full Stack / Backend II (Intern) â€“ United States</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6524e36b7c2e899e</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Application Engineer (FIS Systematics/ ALS)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Oracle, NoSQL, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5f1cd08763c029e</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Cloud BigData Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Delan Associates, Inc</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59ab60d145780389</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Payabli</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76b9fbb8b5a5e806</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Payabli</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62b3077cbdbcc197</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, dbt, Tableau, CI/CD, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bc2fb0114a4b756</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Loudoun County, VA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Leesburg, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Oracle, SQL Server, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e717b40d7b736c3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - Search, Personalization, Agents (Remote)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, ECS, Spark, PySpark, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddc2a574dcde1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer &amp; Architect</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a8133abe73abd87</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Cloud Data Architect</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2808acc4527a33da</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=995dd503c97eb758</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>.Net Architect</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94999510187cc616</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Engineer .NET</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0c3fa28fe6f12d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Distributed Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2c7d9f49e82eee4</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>Everforth ECS</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Arlington, VA, US USA</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D125" t="n">
         <v>10.4</v>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a7c91ca59322d0ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Havenpark Communities</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Orem, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08a26f25fa395039</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-25.xlsx
+++ b/results/job_matches_2026-09-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Magento Architect</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=146beab3fdc4d479</t>
+          <t>https://www.indeed.com/viewjob?jk=ead4b68158e99617</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, PySpark, AWS)</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, Kinesis, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec4e00003379849</t>
+          <t>https://www.indeed.com/viewjob?jk=c67c66a96765b220</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Magento Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Data Modeling, ELT, MLflow</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a436017e20a9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=146beab3fdc4d479</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 4 (Python, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,15 +618,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea69319765aa1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec4e00003379849</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Data Modeling, ELT, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2287ae354f1f523a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a436017e20a9af4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddd1a1b90b2718b</t>
+          <t>https://www.indeed.com/viewjob?jk=fea69319765aa1cc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Personify Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f159b8174b6d797</t>
+          <t>https://www.indeed.com/viewjob?jk=2287ae354f1f523a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b1ed692066ba92</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddd1a1b90b2718b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Personify Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,172 +811,172 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5752c0fe726daa2e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f159b8174b6d797</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Product Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Data Factory, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c24c8142ac8427</t>
+          <t>https://www.indeed.com/viewjob?jk=1df78b8aaf3679cc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mobilunity</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, BigQuery, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02158bbc6c5b14c</t>
+          <t>https://www.indeed.com/viewjob?jk=06a3e07d7bd216c1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Information Data Architect (HYBRID)</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Howell, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c604ade259ccaa</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b1ed692066ba92</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Information Data Architect (HYBRID)</t>
+          <t>Software Engineer-Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Windsor, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ebf151550d94c</t>
+          <t>https://www.indeed.com/viewjob?jk=96d6f3a23638523d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate Information Data Architect (HYBRID)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7ae1d0f1d7773c</t>
+          <t>https://www.indeed.com/viewjob?jk=5752c0fe726daa2e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Product Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Data Factory, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f466c8c66d72247</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c24c8142ac8427</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate Information Data Architect (HYBRID)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Mobilunity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, BigQuery, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af1d8c0bb95e882</t>
+          <t>https://www.indeed.com/viewjob?jk=a02158bbc6c5b14c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Associate Information Data Architect (HYBRID)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Howell, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de31c40d2a0ecf08</t>
+          <t>https://www.indeed.com/viewjob?jk=68c604ade259ccaa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer – Physical AI Platform</t>
+          <t>Associate Information Data Architect (HYBRID)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Windsor, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292f16b23875be76</t>
+          <t>https://www.indeed.com/viewjob?jk=118ebf151550d94c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Information Data Architect (HYBRID)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d939162f62431c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7ae1d0f1d7773c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Associate Information Data Architect (HYBRID)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apex Companies, LLC</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b824421b414861d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5af1d8c0bb95e882</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c65ed1f8238807</t>
+          <t>https://www.indeed.com/viewjob?jk=de31c40d2a0ecf08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,287 +1256,287 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, ETL, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5602865a9185ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ad36cd86055a44</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
+          <t>https://www.indeed.com/viewjob?jk=224df3f1a9ee79b8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Skanska</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d57fb86a5ed9c4</t>
+          <t>https://www.indeed.com/viewjob?jk=7055be6d8f9a7387</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af48e8af3978cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d8c98cbbde5e5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Financial Systems (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4cee9cb47e0f3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cf28aa480065b669</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Architect, Healthcare Payer Domain</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed88a3a19664a4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=944cc70dff5af5ad</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer Sr (ETL/Alteryx)</t>
+          <t>Data Engineer – Physical AI Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=292f16b23875be76</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Tableau, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5662b2a7e9c297d</t>
+          <t>https://www.indeed.com/viewjob?jk=d939162f62431c6d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Apex Companies, LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15797458cef00167</t>
+          <t>https://www.indeed.com/viewjob?jk=b824421b414861d1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5602865a9185ab</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b5f5f93a058e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Skanska</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902a69e0fc5e870</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d57fb86a5ed9c4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Partner Solutions Architect – GSI</t>
+          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wiz Soluções</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8072ceac30ce67e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5af48e8af3978cdd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Business Analyst, Applied Intelligence</t>
+          <t>Sr. Data Engineer, Financial Systems (Remote)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,54 +1721,54 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
+          <t>https://www.indeed.com/viewjob?jk=d4cee9cb47e0f3e3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Architect</t>
+          <t>Senior Architect, Healthcare Payer Domain</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hirschi Companies, LLC</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>North Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Star Schema, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ea9ea264ebb9e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ed88a3a19664a4ab</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps</t>
+          <t>Data Engineer Sr (ETL/Alteryx)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AltexSoft</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,38 +1777,38 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a491606b996c9fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba91948089d6225f</t>
+          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Backend Engineer, Connected Vehicle &amp; Telematics (GCP)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Scala, ETL, CI/CD</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, PostgreSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac2005fd12c4ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc0d2abdbe910d6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate DevOps Engineer</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,112 +1886,112 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0b22901658da1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5662b2a7e9c297d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Engineer, Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ｃollective</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Data Modeling, Dimensional Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020174f364165c18</t>
+          <t>https://www.indeed.com/viewjob?jk=131728c21bda1a28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Platform Engineer</t>
+          <t>Jobs for you</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, DataOps, GitHub Actions</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
+          <t>https://www.indeed.com/viewjob?jk=15797458cef00167</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>POSH</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec04f06f37703a72</t>
+          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sibanye Stillwater</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fairless Hills, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=980adf77ba3c35d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0902a69e0fc5e870</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Partner Solutions Architect – GSI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Wiz Soluções</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Edwardsville, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15662d40b4bb4797</t>
+          <t>https://www.indeed.com/viewjob?jk=8072ceac30ce67e5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Business Analyst, Applied Intelligence</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Star Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652bceb12bdc8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Enterprise Data &amp; AI Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Hirschi Companies, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Star Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0e14623092813</t>
+          <t>https://www.indeed.com/viewjob?jk=9ea9ea264ebb9e6f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfd599f9976074a</t>
+          <t>https://www.indeed.com/viewjob?jk=ba91948089d6225f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ceb5e692edcab9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac2005fd12c4ec8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Associate DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70c97558041cbb3</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0b22901658da1c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>AI Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Ｃollective</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Data Modeling, Dimensional Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44465103a210f6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=020174f364165c18</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Senior Full Stack and Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2b9d01e6a420aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ecebecfe672f7c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer(Azure) at Major Japanese Bank</t>
+          <t>Microsoft Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, DataOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd631b20e53bc138</t>
+          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>POSH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, dbt, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac853620a7883a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec04f06f37703a72</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Data Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Sibanye Stillwater</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fairless Hills, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d60ea38d35340ba</t>
+          <t>https://www.indeed.com/viewjob?jk=980adf77ba3c35d4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer (175879)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Edwardsville, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
+          <t>https://www.indeed.com/viewjob?jk=15662d40b4bb4797</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Skanska</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, SQL Server, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a5364385227f4cc</t>
+          <t>https://www.indeed.com/viewjob?jk=652bceb12bdc8ca1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- full stack Java</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=390092f6c0217007</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0e14623092813</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8918c1adb526db</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfd599f9976074a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Microservices</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ed0115e6583c60</t>
+          <t>https://www.indeed.com/viewjob?jk=83ceb5e692edcab9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Microservices</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Kafka, MLOps, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb4540fc449cc54</t>
+          <t>https://www.indeed.com/viewjob?jk=d70c97558041cbb3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack Applications (Python &amp; React)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, NoSQL, dbt, Amazon QuickSight, Power BI, MLOps, CI/CD, Terraform</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab6da126dcb613</t>
+          <t>https://www.indeed.com/viewjob?jk=44465103a210f6ed</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Service Developer</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, GCP, Scala, Snowflake, NoSQL, ETL, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac560d1fcf55c4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2b9d01e6a420aa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Data Engineer(Azure) at Major Japanese Bank</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd631b20e53bc138</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Python, AWS, Spark)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b838d14974b57715</t>
+          <t>https://www.indeed.com/viewjob?jk=ac853620a7883a2f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer- full stack Java</t>
+          <t>AI Data Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,54 +2806,54 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f81aa15390f51b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d60ea38d35340ba</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (175879)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Oats Overnight</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a248bb83a45531e</t>
+          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Skanska</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,151 +2862,151 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, MicroStrategy, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
+          <t>https://www.indeed.com/viewjob?jk=3a5364385227f4cc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer- full stack Java</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695ee016a6862deb</t>
+          <t>https://www.indeed.com/viewjob?jk=390092f6c0217007</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74dc88aa87ede3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8918c1adb526db</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist New College Grad- Bachelor's/Master's (Austin, TX)</t>
+          <t>AWS Application Support Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Kafka, SQL Server, PostgreSQL, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4dc7483cb11054</t>
+          <t>https://www.indeed.com/viewjob?jk=27ae1f61d818d5de</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AWS Cloud Infrastructure</t>
+          <t>Senior Software Engineer, Full-Stack Applications (Python &amp; React)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines, Inc.</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Spark, Scala, NoSQL, dbt, Amazon QuickSight, Power BI, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42296d5e5f61808</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab6da126dcb613</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Engineer 4 (Cloud Security for Multi Cloud) (Cloud Operations Resilience Engineering)</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465e90d49deb28c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Full-Stack Engineer 4 (Java, Python, AWS, Spark)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=b838d14974b57715</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IT Developer Engineer</t>
+          <t>Software Engineer- full stack Java</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc9fb81e98d2ad5</t>
+          <t>https://www.indeed.com/viewjob?jk=66f81aa15390f51b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Java Spring Boot Developer (FTE / Hybrid)</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, MicroStrategy, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323842bd0f86343f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4c01cee06410c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer 1 4P/846</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Forest Park, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c5956a500a065e</t>
+          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IT Data Solutions Developer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1f8022341fbeec</t>
+          <t>https://www.indeed.com/viewjob?jk=e1919471b72d0ae9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0315e75878b9523</t>
+          <t>https://www.indeed.com/viewjob?jk=695ee016a6862deb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=206f2f5d1f1047a7</t>
+          <t>https://www.indeed.com/viewjob?jk=74dc88aa87ede3c8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Data Scientist New College Grad- Bachelor's/Master's (Austin, TX)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce4fb53c85b4ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=de4dc7483cb11054</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS, CI/CD, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Senior Software Engineer, AWS Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Praxis Precision Medicines, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd4877047c7d1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f42296d5e5f61808</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f51686d020df00d</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Senior QA Engineer (L4)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4dabfb5c32f0281</t>
+          <t>https://www.indeed.com/viewjob?jk=80556d2d1b3dfabf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Node, TypeScript, AWS)</t>
+          <t>Senior Java Spring Boot Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d12d10b908918fa</t>
+          <t>https://www.indeed.com/viewjob?jk=323842bd0f86343f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc673ca517807c08</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4c01cee06410c3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Visualization Engineer 1 4P/846</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Forest Park, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c8a5b6d5542fa2c</t>
+          <t>https://www.indeed.com/viewjob?jk=32c5956a500a065e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb745dca3323ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0315e75878b9523</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5892e9800b1f76b</t>
+          <t>https://www.indeed.com/viewjob?jk=206f2f5d1f1047a7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Go, CI/CD, AWS)</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f69dde706e3448</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce4fb53c85b4ee0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS, CI/CD, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d4dc84b85c3670</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd4877047c7d1ba</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9888eedf29cfd51f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f51686d020df00d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java/Python, IaC, AWS)</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cadf1933502029</t>
+          <t>https://www.indeed.com/viewjob?jk=c4dabfb5c32f0281</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Node, TypeScript, AWS)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843ce198c1c04576</t>
+          <t>https://www.indeed.com/viewjob?jk=2d12d10b908918fa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04ef4604e476c6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc673ca517807c08</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecc6c5f25f41ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=7c8a5b6d5542fa2c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48d24e36571ac6e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb745dca3323ff8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Bank Tech)</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2a2c8569c5046b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5892e9800b1f76b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Full-stack Engineer 4 (Java, Go, CI/CD, AWS)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e410790f9b462e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f69dde706e3448</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52108bbcbb003e69</t>
+          <t>https://www.indeed.com/viewjob?jk=53d4dc84b85c3670</t>
         </is>
       </c>
     </row>
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0cdc8d34a934bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9888eedf29cfd51f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Java/Python, IaC, AWS)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,49 +4101,49 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138e060c9ff0d615</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cadf1933502029</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (AI / ML) - Spring 2027</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefb70733fd4805b</t>
+          <t>https://www.indeed.com/viewjob?jk=843ce198c1c04576</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 - Payment Network Partner Experience</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4157,11 +4157,11 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e45723ef8f4f70</t>
+          <t>https://www.indeed.com/viewjob?jk=ff04ef4604e476c6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b731d4dc3bbcac</t>
+          <t>https://www.indeed.com/viewjob?jk=fecc6c5f25f41ffc</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend II (Intern) â€“ United States</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6524e36b7c2e899e</t>
+          <t>https://www.indeed.com/viewjob?jk=d48d24e36571ac6e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Application Engineer (FIS Systematics/ ALS)</t>
+          <t>Full Stack Engineer 4 (Bank Tech)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Oracle, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,54 +4276,54 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f1cd08763c029e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2a2c8569c5046b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cloud BigData Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ab60d145780389</t>
+          <t>https://www.indeed.com/viewjob?jk=e410790f9b462e9f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4332,81 +4332,81 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
+          <t>https://www.indeed.com/viewjob?jk=52108bbcbb003e69</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
+          <t>https://www.indeed.com/viewjob?jk=d0cdc8d34a934bbc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b9fbb8b5a5e806</t>
+          <t>https://www.indeed.com/viewjob?jk=138e060c9ff0d615</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Data Engineer - Python ,AWS, SQL - Remote</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b3077cbdbcc197</t>
+          <t>https://www.indeed.com/viewjob?jk=bfefbbb5df74fffe</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer Intern (AI / ML) - Spring 2027</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, dbt, Tableau, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc2fb0114a4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=aefb70733fd4805b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integration Engineer 4 - Payment Network Partner Experience</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Loudoun County, VA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Oracle, SQL Server, ETL, CI/CD, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e717b40d7b736c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=41e45723ef8f4f70</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - Search, Personalization, Agents (Remote)</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, ECS, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc2a574dcde1540</t>
+          <t>https://www.indeed.com/viewjob?jk=d9b731d4dc3bbcac</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer &amp; Architect</t>
+          <t>Software Engineer Full Stack / Backend II (Intern) â€“ United States</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8133abe73abd87</t>
+          <t>https://www.indeed.com/viewjob?jk=6524e36b7c2e899e</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Cloud BigData Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2808acc4527a33da</t>
+          <t>https://www.indeed.com/viewjob?jk=59ab60d145780389</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dd503c97eb758</t>
+          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>.Net Architect</t>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94999510187cc616</t>
+          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Engineer .NET</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0c3fa28fe6f12d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Distributed Systems Engineer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins, SonarQube, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c7d9f49e82eee4</t>
+          <t>https://www.indeed.com/viewjob?jk=76b9fbb8b5a5e806</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c91ca59322d0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=62b3077cbdbcc197</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Havenpark Communities</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, dbt, Tableau, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a26f25fa395039</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc2fb0114a4b756</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer (Industrial and Physical AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Loudoun County, VA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,17 +4861,402 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Oracle, SQL Server, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05c7e7244739e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e717b40d7b736c3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Cloud/Infra Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>TalentVibe Business Consultancy</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e2d92172304213c</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - Search, Personalization, Agents (Remote)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, ECS, Spark, PySpark, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddc2a574dcde1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer &amp; Architect</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a8133abe73abd87</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Cloud Data Architect</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2808acc4527a33da</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=995dd503c97eb758</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>.Net Architect</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94999510187cc616</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Engineer .NET</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0c3fa28fe6f12d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sr Functional Analyst with Data Connect / Integration</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afd158f889951e37</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Distributed Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2c7d9f49e82eee4</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7c91ca59322d0ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Havenpark Communities</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Orem, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08a26f25fa395039</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-25.xlsx
+++ b/results/job_matches_2026-09-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,165 +503,165 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineer 4 (Python, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead4b68158e99617</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec4e00003379849</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Data Modeling, ELT, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67c66a96765b220</t>
+          <t>https://www.indeed.com/viewjob?jk=6a436017e20a9af4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Magento Architect</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=146beab3fdc4d479</t>
+          <t>https://www.indeed.com/viewjob?jk=ed5929a259b13da0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python, PySpark, AWS)</t>
+          <t>Intern, IT Data Analytics (2027)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hollister Incorporated</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec4e00003379849</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f2045b50523bff</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Data Modeling, ELT, MLflow</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a436017e20a9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=fea69319765aa1cc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea69319765aa1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddd1a1b90b2718b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Personify Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2287ae354f1f523a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f159b8174b6d797</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Big Data - Medical Cost Grouper - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, HBase, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddd1a1b90b2718b</t>
+          <t>https://www.indeed.com/viewjob?jk=10ee7d4f1fc05ba7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Sr. Salesforce Architect / Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Personify Health</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f159b8174b6d797</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa811352fa1aa90</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Software Engineer-Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,374 +846,374 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df78b8aaf3679cc</t>
+          <t>https://www.indeed.com/viewjob?jk=96d6f3a23638523d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a3e07d7bd216c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b1ed692066ba92</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Data Product Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Data Factory, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b1ed692066ba92</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c24c8142ac8427</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer-Remote</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96d6f3a23638523d</t>
+          <t>https://www.indeed.com/viewjob?jk=de31c40d2a0ecf08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5752c0fe726daa2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ad36cd86055a44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Product Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Data Factory, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c24c8142ac8427</t>
+          <t>https://www.indeed.com/viewjob?jk=224df3f1a9ee79b8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mobilunity</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, BigQuery, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02158bbc6c5b14c</t>
+          <t>https://www.indeed.com/viewjob?jk=7055be6d8f9a7387</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Information Data Architect (HYBRID)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Howell, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c604ade259ccaa</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d8c98cbbde5e5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate Information Data Architect (HYBRID)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Windsor, CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ebf151550d94c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf28aa480065b669</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate Information Data Architect (HYBRID)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Adoreal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7ae1d0f1d7773c</t>
+          <t>https://www.indeed.com/viewjob?jk=944cc70dff5af5ad</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate Information Data Architect (HYBRID)</t>
+          <t>Data Engineer – Physical AI Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af1d8c0bb95e882</t>
+          <t>https://www.indeed.com/viewjob?jk=292f16b23875be76</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Apex Companies, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Cassandra, NoSQL, Data Modeling, Talend</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de31c40d2a0ecf08</t>
+          <t>https://www.indeed.com/viewjob?jk=b824421b414861d1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data &amp; AI Intern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ad36cd86055a44</t>
+          <t>https://www.indeed.com/viewjob?jk=47848c785f526698</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>AFTERWORK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>London, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224df3f1a9ee79b8</t>
+          <t>https://www.indeed.com/viewjob?jk=462d1dfaba6a7d7d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7055be6d8f9a7387</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5602865a9185ab</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer (Internal Tools &amp; Platform)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,207 +1371,207 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d8c98cbbde5e5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0c40611e6f1095</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf28aa480065b669</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Adoreal</t>
+          <t>Skanska</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Snowflake, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944cc70dff5af5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d57fb86a5ed9c4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer – Physical AI Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>TWFG Insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Dataflow, Spark, PySpark, Scala, Fact Tables</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292f16b23875be76</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc6da2f4c063d5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer, AI Data Products</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, Spark, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d939162f62431c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=326243a7df349c66</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Apex Companies, LLC</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b824421b414861d1</t>
+          <t>https://www.indeed.com/viewjob?jk=be84cd3bc47c5004</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer, Financial Systems (Remote)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, ETL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,159 +1581,159 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5602865a9185ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d4cee9cb47e0f3e3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
+          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer, Connected Vehicle &amp; Telematics (GCP)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Skanska</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, PostgreSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d57fb86a5ed9c4</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc0d2abdbe910d6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af48e8af3978cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=b5662b2a7e9c297d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Financial Systems (Remote)</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4cee9cb47e0f3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6054cc97ae7070</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Architect, Healthcare Payer Domain</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1742,73 +1742,73 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed88a3a19664a4ab</t>
+          <t>https://www.indeed.com/viewjob?jk=131728c21bda1a28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer Sr (ETL/Alteryx)</t>
+          <t>Jobs for you</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, ETL, CI/CD</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345b0d2b12a75dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=15797458cef00167</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
+          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
+          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Connected Vehicle &amp; Telematics (GCP)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, PostgreSQL, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc0d2abdbe910d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba91948089d6225f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Tableau, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5662b2a7e9c297d</t>
+          <t>https://www.indeed.com/viewjob?jk=0902a69e0fc5e870</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Business Analyst, Applied Intelligence</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Star Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131728c21bda1a28</t>
+          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>Enterprise Data &amp; AI Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Hirschi Companies, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>North Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Star Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15797458cef00167</t>
+          <t>https://www.indeed.com/viewjob?jk=9ea9ea264ebb9e6f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,77 +1991,77 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac2005fd12c4ec8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902a69e0fc5e870</t>
+          <t>https://www.indeed.com/viewjob?jk=c07bb0961c751f3e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Partner Solutions Architect – GSI</t>
+          <t>AI Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wiz Soluções</t>
+          <t>Ｃollective</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Data Modeling, Dimensional Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,199 +2071,199 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8072ceac30ce67e5</t>
+          <t>https://www.indeed.com/viewjob?jk=020174f364165c18</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Business Analyst, Applied Intelligence</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
+          <t>https://www.indeed.com/viewjob?jk=99f2dbc076e5d856</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Architect</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hirschi Companies, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>North Las Vegas, NV, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Star Schema, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ea9ea264ebb9e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6929f0e8b0d467e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba91948089d6225f</t>
+          <t>https://www.indeed.com/viewjob?jk=b55bf5e8aa6a1b00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac2005fd12c4ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b85bc0bda01150</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate DevOps Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0b22901658da1c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a187bc45f903c25</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Data Engineer, Data Platform</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ｃollective</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Data Modeling, Dimensional Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020174f364165c18</t>
+          <t>https://www.indeed.com/viewjob?jk=19ea3b4e869f0b0f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack and Cloud Platform Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ecebecfe672f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9c766c5fed70eb0a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Platform Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, DataOps, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bcda2cd30fd616</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>POSH</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec04f06f37703a72</t>
+          <t>https://www.indeed.com/viewjob?jk=638ef8567418dc48</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sibanye Stillwater</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fairless Hills, PA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=980adf77ba3c35d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1a136d608291b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Edwardsville, IL, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15662d40b4bb4797</t>
+          <t>https://www.indeed.com/viewjob?jk=edd00710707d78e9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652bceb12bdc8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=442e1899472aaaca</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0e14623092813</t>
+          <t>https://www.indeed.com/viewjob?jk=17caa029de510739</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfd599f9976074a</t>
+          <t>https://www.indeed.com/viewjob?jk=42aa0c7cd36d006a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ceb5e692edcab9</t>
+          <t>https://www.indeed.com/viewjob?jk=cab6925d775e203f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70c97558041cbb3</t>
+          <t>https://www.indeed.com/viewjob?jk=d5653e98fb8135f3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44465103a210f6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=687232035e68a0a9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2b9d01e6a420aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8ba9f5f8c57b5360</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer(Azure) at Major Japanese Bank</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd631b20e53bc138</t>
+          <t>https://www.indeed.com/viewjob?jk=7126e5851d589397</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac853620a7883a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a77cfd4f7c6e8001</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Data Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d60ea38d35340ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f59304446412e07c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (175879)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b64c007a0de94064</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Skanska</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a5364385227f4cc</t>
+          <t>https://www.indeed.com/viewjob?jk=86388f3c259eeff8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- full stack Java</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=390092f6c0217007</t>
+          <t>https://www.indeed.com/viewjob?jk=9675f32b4ffa9a13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8918c1adb526db</t>
+          <t>https://www.indeed.com/viewjob?jk=034638488092da65</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Application Support Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Kafka, SQL Server, PostgreSQL, Power BI, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ae1f61d818d5de</t>
+          <t>https://www.indeed.com/viewjob?jk=ac28966ddf697160</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack Applications (Python &amp; React)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, NoSQL, dbt, Amazon QuickSight, Power BI, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab6da126dcb613</t>
+          <t>https://www.indeed.com/viewjob?jk=24729823d8955c30</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=87a502c5ba52e486</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Python, AWS, Spark)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b838d14974b57715</t>
+          <t>https://www.indeed.com/viewjob?jk=a20461db3b55f8e5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer- full stack Java</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,77 +3111,77 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f81aa15390f51b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c63497e49a35949</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, MicroStrategy, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
+          <t>https://www.indeed.com/viewjob?jk=6deed82147b3397a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sentara</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ab915125e1142b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e19c0167b5b707</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1919471b72d0ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=3957c8134eb5449d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695ee016a6862deb</t>
+          <t>https://www.indeed.com/viewjob?jk=131fbd30ebce4b0e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,137 +3331,137 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74dc88aa87ede3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc69f1717479209</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Scientist New College Grad- Bachelor's/Master's (Austin, TX)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4dc7483cb11054</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbd490415ec98b8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AWS Cloud Infrastructure</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42296d5e5f61808</t>
+          <t>https://www.indeed.com/viewjob?jk=de9da7e405560c98</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=d443ab17a64dc4a2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior QA Engineer (L4)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,417 +3471,417 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80556d2d1b3dfabf</t>
+          <t>https://www.indeed.com/viewjob?jk=abe9a8ea39da933e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Java Spring Boot Developer (FTE / Hybrid)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323842bd0f86343f</t>
+          <t>https://www.indeed.com/viewjob?jk=2436088e04cb9418</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4c01cee06410c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4760b3a15e7c28bf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer 1 4P/846</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Forest Park, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c5956a500a065e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a34bf218fa3ecdb</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0315e75878b9523</t>
+          <t>https://www.indeed.com/viewjob?jk=4c29c8279e212129</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=206f2f5d1f1047a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbc6b68160b7f80</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce4fb53c85b4ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=e67361e9400bbca3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS, CI/CD, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd4877047c7d1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=56277a5a14ecfae3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f51686d020df00d</t>
+          <t>https://www.indeed.com/viewjob?jk=64341d28e22d4d4a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4dabfb5c32f0281</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0db3535ef241d9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Node, TypeScript, AWS)</t>
+          <t>Senior Full Stack and Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d12d10b908918fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ecebecfe672f7c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Microsoft Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, DataOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc673ca517807c08</t>
+          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>POSH</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c8a5b6d5542fa2c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec04f06f37703a72</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Edwardsville, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb745dca3323ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=15662d40b4bb4797</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5892e9800b1f76b</t>
+          <t>https://www.indeed.com/viewjob?jk=652bceb12bdc8ca1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Go, CI/CD, AWS)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f69dde706e3448</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0e14623092813</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d4dc84b85c3670</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfd599f9976074a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9888eedf29cfd51f</t>
+          <t>https://www.indeed.com/viewjob?jk=83ceb5e692edcab9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java/Python, IaC, AWS)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cadf1933502029</t>
+          <t>https://www.indeed.com/viewjob?jk=d70c97558041cbb3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843ce198c1c04576</t>
+          <t>https://www.indeed.com/viewjob?jk=44465103a210f6ed</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Software Engineer III - Python, Databricks and AWS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04ef4604e476c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2b9d01e6a420aa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Data Engineer(Azure) at Major Japanese Bank</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>API Gateway, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecc6c5f25f41ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=fd631b20e53bc138</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer (175879)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48d24e36571ac6e</t>
+          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Bank Tech)</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,49 +4276,49 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2a2c8569c5046b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>AWS Application Support Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Kafka, SQL Server, PostgreSQL, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e410790f9b462e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=27ae1f61d818d5de</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-Stack Engineer 4 (Java, Python, AWS, Spark)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4328,15 +4328,15 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52108bbcbb003e69</t>
+          <t>https://www.indeed.com/viewjob?jk=b838d14974b57715</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, MicroStrategy, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0cdc8d34a934bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Software Engineer 1 - Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,42 +4406,42 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=138e060c9ff0d615</t>
+          <t>https://www.indeed.com/viewjob?jk=69fd302298183375</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer - Python ,AWS, SQL - Remote</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfefbbb5df74fffe</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (AI / ML) - Spring 2027</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,242 +4486,242 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefb70733fd4805b</t>
+          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 - Payment Network Partner Experience</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e45723ef8f4f70</t>
+          <t>https://www.indeed.com/viewjob?jk=e1919471b72d0ae9</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b731d4dc3bbcac</t>
+          <t>https://www.indeed.com/viewjob?jk=695ee016a6862deb</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend II (Intern) â€“ United States</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6524e36b7c2e899e</t>
+          <t>https://www.indeed.com/viewjob?jk=74dc88aa87ede3c8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cloud BigData Engineer</t>
+          <t>Data Scientist New College Grad- Bachelor's/Master's (Austin, TX)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ab60d145780389</t>
+          <t>https://www.indeed.com/viewjob?jk=de4dc7483cb11054</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
+          <t>Senior Software Engineer, AWS Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Praxis Precision Medicines, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt, Git, Python</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
+          <t>https://www.indeed.com/viewjob?jk=f42296d5e5f61808</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer - Matterport</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,102 +4731,102 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbdfdc99e931506</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>iDC Logistics</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b9fbb8b5a5e806</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f033dfebaee3ca</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Payabli</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b3077cbdbcc197</t>
+          <t>https://www.indeed.com/viewjob?jk=b8593692b74910cb</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Visualization Engineer 1 4P/846</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Forest Park, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, dbt, Tableau, CI/CD, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,67 +4836,67 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc2fb0114a4b756</t>
+          <t>https://www.indeed.com/viewjob?jk=32c5956a500a065e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Loudoun County, VA</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Oracle, SQL Server, ETL, CI/CD, Git</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e717b40d7b736c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4c01cee06410c3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cloud/Infra Enterprise Architect</t>
+          <t>Senior QA Engineer (L4)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TalentVibe Business Consultancy</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2d92172304213c</t>
+          <t>https://www.indeed.com/viewjob?jk=80556d2d1b3dfabf</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - Search, Personalization, Agents (Remote)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, ECS, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,67 +4941,67 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc2a574dcde1540</t>
+          <t>https://www.indeed.com/viewjob?jk=adb59a064cdc32b3</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer &amp; Architect</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8133abe73abd87</t>
+          <t>https://www.indeed.com/viewjob?jk=206f2f5d1f1047a7</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2808acc4527a33da</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce4fb53c85b4ee0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Full-Stack Engineer 4 (Python, Java, AWS, CI/CD, GenAI) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dd503c97eb758</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd4877047c7d1ba</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>.Net Architect</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94999510187cc616</t>
+          <t>https://www.indeed.com/viewjob?jk=9f51686d020df00d</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Engineer .NET</t>
+          <t>Full Stack Engineer 5</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,67 +5116,67 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0c3fa28fe6f12d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c4dabfb5c32f0281</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr Functional Analyst with Data Connect / Integration</t>
+          <t>Full-stack Engineer 4 (Node, TypeScript, AWS)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd158f889951e37</t>
+          <t>https://www.indeed.com/viewjob?jk=2d12d10b908918fa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Distributed Systems Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c7d9f49e82eee4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc673ca517807c08</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Scala, ETL, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,42 +5221,917 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c91ca59322d0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=7c8a5b6d5542fa2c</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ffb745dca3323ff8</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5892e9800b1f76b</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Java, Go, CI/CD, AWS)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7f69dde706e3448</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53d4dc84b85c3670</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9888eedf29cfd51f</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Java/Python, IaC, AWS)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4cadf1933502029</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f2b3596f51501b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70480a7733a24dbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Data Engineer - Python ,AWS, SQL - Remote</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Redshift, S3, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfefbbb5df74fffe</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (AI / ML) - Spring 2027</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aefb70733fd4805b</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Integration Engineer 4 - Payment Network Partner Experience</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41e45723ef8f4f70</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - VAULT</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9b731d4dc3bbcac</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Cloud BigData Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Delan Associates, Inc</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59ab60d145780389</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt, Git, Python</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Payabli</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76b9fbb8b5a5e806</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Payabli</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62b3077cbdbcc197</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, dbt, Tableau, CI/CD, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bc2fb0114a4b756</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Loudoun County, VA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Leesburg, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Oracle, SQL Server, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e717b40d7b736c3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Fairlife, LLC</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Power BI, Tableau, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3d98d3b46d4d0a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
           <t>AI Solutions Engineer</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>Havenpark Communities</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>Orem, UT, US USA</t>
         </is>
       </c>
-      <c r="D138" t="n">
+      <c r="D159" t="n">
         <v>10.4</v>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=08a26f25fa395039</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Engineer .NET</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0c3fa28fe6f12d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Sr Functional Analyst with Data Connect / Integration</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afd158f889951e37</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Systems Programming Engineer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Mountainside Investment Group, LLC</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Weslaco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2486c4db449718f</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Cloud/Infra Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>TalentVibe Business Consultancy</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e2d92172304213c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-25.xlsx
+++ b/results/job_matches_2026-09-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Integration Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MOXFIVE</t>
+          <t>Everon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,21 +482,21 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, Azure, Synapse Analytics, Databricks, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e682d983ea38fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bf341f814fc4d9</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Product Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>PRADCO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, Data Factory, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c24c8142ac8427</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9009df35d7b57b</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Microsoft Fabric Data Architect / Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apex Companies, LLC</t>
+          <t>Paylink Direct</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b824421b414861d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a08f4b3b3963d2a3</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AFTERWORK</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>London, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462d1dfaba6a7d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b557a1c3d0e30a4a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, ETL, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5602865a9185ab</t>
+          <t>https://www.indeed.com/viewjob?jk=221dce02ae4400cf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Internal Tools &amp; Platform)</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AFTERWORK</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>London, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,94 +1371,94 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0c40611e6f1095</t>
+          <t>https://www.indeed.com/viewjob?jk=462d1dfaba6a7d7d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Magnaflow</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Oceanside, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, NoSQL, Snowflake Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6729a082d816c2d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer (Internal Tools &amp; Platform)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Skanska</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server</t>
+          <t>AWS, Glue, RDS, Spark, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d57fb86a5ed9c4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0c40611e6f1095</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TWFG Insurance</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Dataflow, Spark, PySpark, Scala, Fact Tables</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc6da2f4c063d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa90431a3fa096c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data Engineer, AI Data Products</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lincoln Financial</t>
+          <t>Skanska</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, Spark, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326243a7df349c66</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d57fb86a5ed9c4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>TWFG Insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Dataflow, Spark, PySpark, Scala, Fact Tables</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be84cd3bc47c5004</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc6da2f4c063d5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Financial Systems (Remote)</t>
+          <t>Associate Data Engineer, AI Data Products</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, IAM, RDS, Spark, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4cee9cb47e0f3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=326243a7df349c66</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
+          <t>https://www.indeed.com/viewjob?jk=be84cd3bc47c5004</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Connected Vehicle &amp; Telematics (GCP)</t>
+          <t>Sr. Data Engineer, Financial Systems (Remote)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, PostgreSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc0d2abdbe910d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4cee9cb47e0f3e3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Tableau, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5662b2a7e9c297d</t>
+          <t>https://www.indeed.com/viewjob?jk=998cfb2b283317ea</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer III, Cloud</t>
+          <t>Senior Backend Engineer, Connected Vehicle &amp; Telematics (GCP)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, PostgreSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6054cc97ae7070</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc0d2abdbe910d6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131728c21bda1a28</t>
+          <t>https://www.indeed.com/viewjob?jk=b5662b2a7e9c297d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jobs for you</t>
+          <t>DevOps Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15797458cef00167</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae962c4658819a4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
+          <t>Data Engineer III, Cloud</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Mobis Parts America, LLC.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6054cc97ae7070</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, Kafka, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba91948089d6225f</t>
+          <t>https://www.indeed.com/viewjob?jk=131728c21bda1a28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Jobs for you</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Scala, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902a69e0fc5e870</t>
+          <t>https://www.indeed.com/viewjob?jk=15797458cef00167</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Business Analyst, Applied Intelligence</t>
+          <t>Sr. Engineer - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
+          <t>https://www.indeed.com/viewjob?jk=73de85844ee49e2f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Architect</t>
+          <t>VMware VDI to AWS WorkSpaces Core Migration Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hirschi Companies, LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>North Las Vegas, NV, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Star Schema, ELT, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ea9ea264ebb9e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=78bd9b74a1882f4e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Information Technology Architect | (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>City of Atlanta</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac2005fd12c4ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e657852ef5f740</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, ETL, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,199 +2036,199 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07bb0961c751f3e</t>
+          <t>https://www.indeed.com/viewjob?jk=57742a64192a9c15</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Data Engineer, Data Platform</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ｃollective</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Data Modeling, Dimensional Modeling, dbt, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020174f364165c18</t>
+          <t>https://www.indeed.com/viewjob?jk=945bd3fa6f051f40</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f2dbc076e5d856</t>
+          <t>https://www.indeed.com/viewjob?jk=ba91948089d6225f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6929f0e8b0d467e</t>
+          <t>https://www.indeed.com/viewjob?jk=0902a69e0fc5e870</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55bf5e8aa6a1b00</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac2005fd12c4ec8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Sr Business Analyst, Applied Intelligence</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Star Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b85bc0bda01150</t>
+          <t>https://www.indeed.com/viewjob?jk=6fce8cf621ee0dba</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Hive, Spark, Scala, NoSQL, Data Modeling, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a187bc45f903c25</t>
+          <t>https://www.indeed.com/viewjob?jk=52509eca710cb0dc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior STIBO Software Developer</t>
+          <t>AI DevOps Engineer| Hybrid: Chicago, IL or NYC, NY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ea3b4e869f0b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=c07bb0961c751f3e</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c766c5fed70eb0a</t>
+          <t>https://www.indeed.com/viewjob?jk=99f2dbc076e5d856</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bcda2cd30fd616</t>
+          <t>https://www.indeed.com/viewjob?jk=a6929f0e8b0d467e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638ef8567418dc48</t>
+          <t>https://www.indeed.com/viewjob?jk=b55bf5e8aa6a1b00</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1a136d608291b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b85bc0bda01150</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd00710707d78e9</t>
+          <t>https://www.indeed.com/viewjob?jk=9a187bc45f903c25</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442e1899472aaaca</t>
+          <t>https://www.indeed.com/viewjob?jk=19ea3b4e869f0b0f</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17caa029de510739</t>
+          <t>https://www.indeed.com/viewjob?jk=9c766c5fed70eb0a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42aa0c7cd36d006a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bcda2cd30fd616</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab6925d775e203f</t>
+          <t>https://www.indeed.com/viewjob?jk=638ef8567418dc48</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5653e98fb8135f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1a136d608291b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=687232035e68a0a9</t>
+          <t>https://www.indeed.com/viewjob?jk=edd00710707d78e9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ba9f5f8c57b5360</t>
+          <t>https://www.indeed.com/viewjob?jk=442e1899472aaaca</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7126e5851d589397</t>
+          <t>https://www.indeed.com/viewjob?jk=17caa029de510739</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77cfd4f7c6e8001</t>
+          <t>https://www.indeed.com/viewjob?jk=42aa0c7cd36d006a</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59304446412e07c</t>
+          <t>https://www.indeed.com/viewjob?jk=cab6925d775e203f</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64c007a0de94064</t>
+          <t>https://www.indeed.com/viewjob?jk=d5653e98fb8135f3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86388f3c259eeff8</t>
+          <t>https://www.indeed.com/viewjob?jk=687232035e68a0a9</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675f32b4ffa9a13</t>
+          <t>https://www.indeed.com/viewjob?jk=8ba9f5f8c57b5360</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034638488092da65</t>
+          <t>https://www.indeed.com/viewjob?jk=7126e5851d589397</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac28966ddf697160</t>
+          <t>https://www.indeed.com/viewjob?jk=a77cfd4f7c6e8001</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24729823d8955c30</t>
+          <t>https://www.indeed.com/viewjob?jk=f59304446412e07c</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87a502c5ba52e486</t>
+          <t>https://www.indeed.com/viewjob?jk=b64c007a0de94064</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20461db3b55f8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=86388f3c259eeff8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c63497e49a35949</t>
+          <t>https://www.indeed.com/viewjob?jk=9675f32b4ffa9a13</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6deed82147b3397a</t>
+          <t>https://www.indeed.com/viewjob?jk=034638488092da65</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ab915125e1142b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac28966ddf697160</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e19c0167b5b707</t>
+          <t>https://www.indeed.com/viewjob?jk=24729823d8955c30</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3957c8134eb5449d</t>
+          <t>https://www.indeed.com/viewjob?jk=87a502c5ba52e486</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131fbd30ebce4b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=a20461db3b55f8e5</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc69f1717479209</t>
+          <t>https://www.indeed.com/viewjob?jk=3c63497e49a35949</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbd490415ec98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6deed82147b3397a</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9da7e405560c98</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ab915125e1142b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d443ab17a64dc4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e19c0167b5b707</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe9a8ea39da933e</t>
+          <t>https://www.indeed.com/viewjob?jk=3957c8134eb5449d</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2436088e04cb9418</t>
+          <t>https://www.indeed.com/viewjob?jk=131fbd30ebce4b0e</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4760b3a15e7c28bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc69f1717479209</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a34bf218fa3ecdb</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbd490415ec98b8</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c29c8279e212129</t>
+          <t>https://www.indeed.com/viewjob?jk=de9da7e405560c98</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbc6b68160b7f80</t>
+          <t>https://www.indeed.com/viewjob?jk=d443ab17a64dc4a2</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67361e9400bbca3</t>
+          <t>https://www.indeed.com/viewjob?jk=abe9a8ea39da933e</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56277a5a14ecfae3</t>
+          <t>https://www.indeed.com/viewjob?jk=2436088e04cb9418</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64341d28e22d4d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4760b3a15e7c28bf</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0db3535ef241d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a34bf218fa3ecdb</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Full Stack and Cloud Platform Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ecebecfe672f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c29c8279e212129</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Platform Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, DataOps, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
+          <t>https://www.indeed.com/viewjob?jk=0dbc6b68160b7f80</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>POSH</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec04f06f37703a72</t>
+          <t>https://www.indeed.com/viewjob?jk=e67361e9400bbca3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Edwardsville, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15662d40b4bb4797</t>
+          <t>https://www.indeed.com/viewjob?jk=56277a5a14ecfae3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652bceb12bdc8ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=64341d28e22d4d4a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior STIBO Software Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0e14623092813</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0db3535ef241d9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Full Stack and Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfd599f9976074a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ecebecfe672f7c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Microsoft Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, DataOps, GitHub Actions</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ceb5e692edcab9</t>
+          <t>https://www.indeed.com/viewjob?jk=216ef2a06cb05f06</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>POSH</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70c97558041cbb3</t>
+          <t>https://www.indeed.com/viewjob?jk=ec04f06f37703a72</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer (175879)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44465103a210f6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Databricks and AWS</t>
+          <t>Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,29 +4161,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2b9d01e6a420aa</t>
+          <t>https://www.indeed.com/viewjob?jk=85eff740f1ceace8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer(Azure) at Major Japanese Bank</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4192,98 +4192,98 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Data Factory, Databricks, Spark, PySpark, NoSQL, ETL, ELT</t>
+          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, MicroStrategy, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd631b20e53bc138</t>
+          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer (175879)</t>
+          <t>Software Engineer 1 - Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Scala, Snowflake, dbt, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c9cd63529737fa</t>
+          <t>https://www.indeed.com/viewjob?jk=69fd302298183375</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6cfd02d9826aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AWS Application Support Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4297,11 +4297,11 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Kafka, SQL Server, PostgreSQL, Power BI, Splunk</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,59 +4311,59 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ae1f61d818d5de</t>
+          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Python, AWS, Spark)</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>vertage</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b838d14974b57715</t>
+          <t>https://www.indeed.com/viewjob?jk=e1919471b72d0ae9</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, GCP, Hadoop, Hive, Spark, Scala, MicroStrategy, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb797238596b5283</t>
+          <t>https://www.indeed.com/viewjob?jk=695ee016a6862deb</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Kiewit Technology Group</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fd302298183375</t>
+          <t>https://www.indeed.com/viewjob?jk=74dc88aa87ede3c8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sentara</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Norfolk, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,17 +4441,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0364757c79beba</t>
+          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
         </is>
       </c>
     </row>
@@ -4463,12 +4463,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Ezee Fiber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, PostgreSQL, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d893afa2af62f4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=14553b87b9e8856d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>vertage</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1919471b72d0ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=ddff3d8fcac07d3a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer - Matterport</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695ee016a6862deb</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbdfdc99e931506</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Associate Data Engineer, AI Data Products</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Spark, Snowflake, PostgreSQL, NoSQL, Data Modeling, ETL, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Athena, API Gateway, ECS, IAM, RDS, dbt, MLOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74dc88aa87ede3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=63821a0502f55779</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Scientist New College Grad- Bachelor's/Master's (Austin, TX)</t>
+          <t>Analytics Engineer (Power BI)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4dc7483cb11054</t>
+          <t>https://www.indeed.com/viewjob?jk=6d65655a9bdf8af8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AWS Cloud Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines, Inc.</t>
+          <t>iDC Logistics</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, dbt</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42296d5e5f61808</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f033dfebaee3ca</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Business Intelligence Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9642665184944e11</t>
+          <t>https://www.indeed.com/viewjob?jk=13861c16b28c1ecd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Matterport</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbdfdc99e931506</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4c01cee06410c3</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>iDC Logistics</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, dbt</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f033dfebaee3ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b8593692b74910cb</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Visualization Engineer 1 4P/846</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>Forest Park, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8593692b74910cb</t>
+          <t>https://www.indeed.com/viewjob?jk=32c5956a500a065e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer 1 4P/846</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Forest Park, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c5956a500a065e</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc24126bb01a3b5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>DevSecOps Security Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4c01cee06410c3</t>
+          <t>https://www.indeed.com/viewjob?jk=21206c796173cd36</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior QA Engineer (L4)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,14 +4906,14 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80556d2d1b3dfabf</t>
+          <t>https://www.indeed.com/viewjob?jk=adb59a064cdc32b3</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4941,14 +4941,14 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb59a064cdc32b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2b3596f51501b1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4971,89 +4971,89 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=206f2f5d1f1047a7</t>
+          <t>https://www.indeed.com/viewjob?jk=70480a7733a24dbb</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Data Engineer - Python ,AWS, SQL - Remote</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce4fb53c85b4ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=bfefbbb5df74fffe</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, Java, AWS, CI/CD, GenAI) (Enterprise Platforms Technology)</t>
+          <t>Software Engineer Intern (AI / ML) - Spring 2027</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd4877047c7d1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=aefb70733fd4805b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Integration Engineer 4 - Payment Network Partner Experience</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5063,15 +5063,15 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,242 +5081,242 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f51686d020df00d</t>
+          <t>https://www.indeed.com/viewjob?jk=41e45723ef8f4f70</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 5</t>
+          <t>Cloud BigData Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4dabfb5c32f0281</t>
+          <t>https://www.indeed.com/viewjob?jk=59ab60d145780389</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Node, TypeScript, AWS)</t>
+          <t>Sr. Data and Platform Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, PySpark, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d12d10b908918fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b516dee5bebdf7</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Associate Cloud Data Engineer - EDW Team</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>G.E.H.A</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lee's Summit, MO, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc673ca517807c08</t>
+          <t>https://www.indeed.com/viewjob?jk=eda83b90519c1a63</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt, Git, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c8a5b6d5542fa2c</t>
+          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb745dca3323ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5892e9800b1f76b</t>
+          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Go, CI/CD, AWS)</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f69dde706e3448</t>
+          <t>https://www.indeed.com/viewjob?jk=76b9fbb8b5a5e806</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Payabli</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d4dc84b85c3670</t>
+          <t>https://www.indeed.com/viewjob?jk=62b3077cbdbcc197</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Scala, dbt, Tableau, CI/CD, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,59 +5396,59 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9888eedf29cfd51f</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc2fb0114a4b756</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java/Python, IaC, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cadf1933502029</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdece1225c2c990</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2b3596f51501b1</t>
+          <t>https://www.indeed.com/viewjob?jk=858fa984b328a939</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4- People Tech- GenAI &amp; Agentic Systems (LangChain, LangGraph)</t>
+          <t>Senior Data Analyst (Gas Engineering)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>National Grid</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70480a7733a24dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=a54d2ee50c8485d9</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer - Python ,AWS, SQL - Remote</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Havenpark Communities</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfefbbb5df74fffe</t>
+          <t>https://www.indeed.com/viewjob?jk=08a26f25fa395039</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (AI / ML) - Spring 2027</t>
+          <t>Sr Functional Analyst with Data Connect / Integration</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefb70733fd4805b</t>
+          <t>https://www.indeed.com/viewjob?jk=afd158f889951e37</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Integration Engineer 4 - Payment Network Partner Experience</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Power BI, Tableau, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e45723ef8f4f70</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d98d3b46d4d0a8</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Cloud/Infra Enterprise Architect</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>TalentVibe Business Consultancy</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,505 +5631,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b731d4dc3bbcac</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Cloud BigData Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Delan Associates, Inc</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59ab60d145780389</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>AI Data Engineer Intern - QuantumBlack, AI by McKinsey</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>McKinsey &amp; Company</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt, Git, Python</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1697413820124a26</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29fad152308282f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Wichita, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7239eb247bd719da</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Payabli</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76b9fbb8b5a5e806</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Payabli</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62b3077cbdbcc197</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, dbt, Tableau, CI/CD, Airflow, Apache Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc2fb0114a4b756</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Loudoun County, VA</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Leesburg, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Oracle, SQL Server, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e717b40d7b736c3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Fairlife, LLC</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Power BI, Tableau, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d98d3b46d4d0a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>AI Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Havenpark Communities</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Orem, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08a26f25fa395039</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Senior Engineer .NET</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0c3fa28fe6f12d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Sr Functional Analyst with Data Connect / Integration</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afd158f889951e37</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Systems Programming Engineer</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Mountainside Investment Group, LLC</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Weslaco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2486c4db449718f</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Cloud/Infra Enterprise Architect</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>TalentVibe Business Consultancy</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0e2d92172304213c</t>
         </is>
